--- a/GATEWAY/S1#111#JOINSOFTSRLXX/Joinsoft_Srl/Gestione_Stabilimenti_Termali/Ver_6.31/report-checklist.xlsx
+++ b/GATEWAY/S1#111#JOINSOFTSRLXX/Joinsoft_Srl/Gestione_Stabilimenti_Termali/Ver_6.31/report-checklist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francesco\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBA5A7F-529B-41D1-916B-279B990DC980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE373560-8C7C-4553-BB0A-5A2B3BD6F4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3075" yWindow="-13620" windowWidth="21840" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -1948,24 +1948,6 @@
     <t>Messaggio errore: ERROR: -1,-1 cvc-complex-type.2.4.a: Invalid content was found starting with element '{"urn:hl7-org:v3":languageCode}'. One of '{"urn:hl7-org:v3":confidentialityCode}' is expected.</t>
   </si>
   <si>
-    <t>2025-12-06T08:15:08.892Z</t>
-  </si>
-  <si>
-    <t>a5334577f3ad6c647affc5627f15351a</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.0cf259caff118127d861d5a0a3320b3f8d15aea12c68869b2da55e741ccd9bed.a597f1d300^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2025-12-06T08:15:10.147Z</t>
-  </si>
-  <si>
-    <t>16d0623a4b28136f318b18cdb0226d70</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.8524cd59576a8fb7893ba4754928692a82384dff11affb0cf77b82267861b014.d78983fb7d^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>2025-12-06T08:15:11.221Z</t>
   </si>
   <si>
@@ -2155,24 +2137,6 @@
     <t>Messaggio errore: [ERRORE-30| L'elemento ClinicalDocument/legalAuthenticator/signatureCode deve essere valorizzato con il codice "S" ]</t>
   </si>
   <si>
-    <t>2025-12-06T08:14:43.466Z</t>
-  </si>
-  <si>
-    <t>aead3ded5efaf3a8854f18ce53590008</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.b3cea481b85985332cd8272f91659ddc3e8ab74f1984ac63a6aa93d38bcff853.062fc124bb^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2025-12-06T08:14:44.946Z</t>
-  </si>
-  <si>
-    <t>4b5ad19237ac0202e64275af420d0ff3</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.cef503f3ac57f62be58b0318ffbc49f77369a28d8ef8cade00efa2d30b6320aa.82c4922317^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>2025-12-06T08:14:46.106Z</t>
   </si>
   <si>
@@ -2243,6 +2207,42 @@
   </si>
   <si>
     <t>96ba6135629f789eb2778a43f8b6c7d7</t>
+  </si>
+  <si>
+    <t>2026-03-06T15:51:09.943Z</t>
+  </si>
+  <si>
+    <t>aac2e7cb1c7c3220122b8f591a73f015</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.f7b894b3a81cc99665fc11da1b86dda52777a974623d939bd318c0d392bee9da.78152d74d0^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-06T15:51:11.318Z</t>
+  </si>
+  <si>
+    <t>33bc6c11aa1433ec8659f2ee16c2a8f5</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.dfe47c5b669ed6d03ff3e464f0b7a7ddb65109bf84965676e19a287e378c758e.b3c02e9078^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-06T15:51:13.077Z</t>
+  </si>
+  <si>
+    <t>ae502d87b446230ce2bc7347fb7ad747</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.117789eb8e22f6c94d31a40b7b9b3f5c4589c6c9ab03133d13360782f1b8a150.8c45f7d9bc^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-06T15:51:14.652Z</t>
+  </si>
+  <si>
+    <t>af1a8db82c7ecf940c9729bf84976d15</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.4175a3ea5c2a8ebacb9146e63da90f5141633abd7cbb86ef4630d25f17280334.6dc48e4501^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="B2" s="53"/>
       <c r="C2" s="54" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="D2" s="53"/>
       <c r="F2" s="6"/>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B3" s="56"/>
       <c r="C3" s="61" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="D3" s="53"/>
       <c r="F3" s="6"/>
@@ -4428,7 +4428,7 @@
       <c r="A4" s="57"/>
       <c r="B4" s="58"/>
       <c r="C4" s="61" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="D4" s="53"/>
       <c r="E4" s="4"/>
@@ -4455,7 +4455,7 @@
       <c r="A5" s="59"/>
       <c r="B5" s="60"/>
       <c r="C5" s="61" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="D5" s="53"/>
       <c r="F5" s="6"/>
@@ -4641,7 +4641,7 @@
         <v>235</v>
       </c>
       <c r="L10" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M10" s="38"/>
       <c r="N10" s="38"/>
@@ -4684,7 +4684,7 @@
         <v>235</v>
       </c>
       <c r="L11" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M11" s="38"/>
       <c r="N11" s="38"/>
@@ -4727,7 +4727,7 @@
         <v>235</v>
       </c>
       <c r="L12" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M12" s="38"/>
       <c r="N12" s="38"/>
@@ -4770,7 +4770,7 @@
         <v>235</v>
       </c>
       <c r="L13" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M13" s="38"/>
       <c r="N13" s="38"/>
@@ -4786,7 +4786,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" ht="11.1" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="35">
         <v>31</v>
       </c>
@@ -4806,10 +4806,10 @@
         <v>45997</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="I14" s="42" t="s">
         <v>439</v>
@@ -4867,10 +4867,10 @@
         <v>45997</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="I15" s="42" t="s">
         <v>439</v>
@@ -4935,7 +4935,7 @@
         <v>235</v>
       </c>
       <c r="L16" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M16" s="38"/>
       <c r="N16" s="38"/>
@@ -4978,7 +4978,7 @@
         <v>235</v>
       </c>
       <c r="L17" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M17" s="38"/>
       <c r="N17" s="38"/>
@@ -5021,7 +5021,7 @@
         <v>235</v>
       </c>
       <c r="L18" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M18" s="38"/>
       <c r="N18" s="38"/>
@@ -5064,7 +5064,7 @@
         <v>235</v>
       </c>
       <c r="L19" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M19" s="38"/>
       <c r="N19" s="38"/>
@@ -5107,7 +5107,7 @@
         <v>235</v>
       </c>
       <c r="L20" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M20" s="38"/>
       <c r="N20" s="38"/>
@@ -5150,7 +5150,7 @@
         <v>235</v>
       </c>
       <c r="L21" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M21" s="38"/>
       <c r="N21" s="38"/>
@@ -5166,7 +5166,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:23" ht="11.1" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="35">
         <v>39</v>
       </c>
@@ -5186,10 +5186,10 @@
         <v>45997</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="I22" s="42" t="s">
         <v>439</v>
@@ -5247,10 +5247,10 @@
         <v>45997</v>
       </c>
       <c r="G23" s="37" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="I23" s="42" t="s">
         <v>439</v>
@@ -5315,7 +5315,7 @@
         <v>235</v>
       </c>
       <c r="L24" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M24" s="38"/>
       <c r="N24" s="38"/>
@@ -5358,7 +5358,7 @@
         <v>235</v>
       </c>
       <c r="L25" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M25" s="38"/>
       <c r="N25" s="38"/>
@@ -5401,7 +5401,7 @@
         <v>235</v>
       </c>
       <c r="L26" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M26" s="38"/>
       <c r="N26" s="38"/>
@@ -5444,7 +5444,7 @@
         <v>235</v>
       </c>
       <c r="L27" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M27" s="38" t="s">
         <v>64</v>
@@ -5501,7 +5501,7 @@
         <v>235</v>
       </c>
       <c r="L28" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M28" s="38" t="s">
         <v>64</v>
@@ -5558,7 +5558,7 @@
         <v>235</v>
       </c>
       <c r="L29" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M29" s="38" t="s">
         <v>64</v>
@@ -5665,13 +5665,13 @@
         <v>45997</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="I31" s="42" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="J31" s="38" t="s">
         <v>64</v>
@@ -5735,7 +5735,7 @@
         <v>235</v>
       </c>
       <c r="L32" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M32" s="38" t="s">
         <v>64</v>
@@ -5792,7 +5792,7 @@
         <v>235</v>
       </c>
       <c r="L33" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M33" s="38" t="s">
         <v>64</v>
@@ -5849,7 +5849,7 @@
         <v>235</v>
       </c>
       <c r="L34" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M34" s="38" t="s">
         <v>64</v>
@@ -5906,7 +5906,7 @@
         <v>235</v>
       </c>
       <c r="L35" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M35" s="38"/>
       <c r="N35" s="38"/>
@@ -5949,7 +5949,7 @@
         <v>235</v>
       </c>
       <c r="L36" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M36" s="38"/>
       <c r="N36" s="38"/>
@@ -5992,7 +5992,7 @@
         <v>235</v>
       </c>
       <c r="L37" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M37" s="38"/>
       <c r="N37" s="38"/>
@@ -6035,7 +6035,7 @@
         <v>235</v>
       </c>
       <c r="L38" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M38" s="38"/>
       <c r="N38" s="38"/>
@@ -6078,7 +6078,7 @@
         <v>235</v>
       </c>
       <c r="L39" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M39" s="38"/>
       <c r="N39" s="38"/>
@@ -6121,7 +6121,7 @@
         <v>235</v>
       </c>
       <c r="L40" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M40" s="38"/>
       <c r="N40" s="38"/>
@@ -6164,7 +6164,7 @@
         <v>235</v>
       </c>
       <c r="L41" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M41" s="38"/>
       <c r="N41" s="38"/>
@@ -6207,7 +6207,7 @@
         <v>235</v>
       </c>
       <c r="L42" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M42" s="38"/>
       <c r="N42" s="38"/>
@@ -6250,7 +6250,7 @@
         <v>235</v>
       </c>
       <c r="L43" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M43" s="38"/>
       <c r="N43" s="38"/>
@@ -6293,7 +6293,7 @@
         <v>235</v>
       </c>
       <c r="L44" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M44" s="38"/>
       <c r="N44" s="38"/>
@@ -6336,7 +6336,7 @@
         <v>235</v>
       </c>
       <c r="L45" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M45" s="38"/>
       <c r="N45" s="38"/>
@@ -6379,7 +6379,7 @@
         <v>235</v>
       </c>
       <c r="L46" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M46" s="38"/>
       <c r="N46" s="38"/>
@@ -6422,7 +6422,7 @@
         <v>235</v>
       </c>
       <c r="L47" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M47" s="38"/>
       <c r="N47" s="38"/>
@@ -6465,7 +6465,7 @@
         <v>235</v>
       </c>
       <c r="L48" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M48" s="38"/>
       <c r="N48" s="38"/>
@@ -6508,7 +6508,7 @@
         <v>235</v>
       </c>
       <c r="L49" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M49" s="38"/>
       <c r="N49" s="38"/>
@@ -6551,7 +6551,7 @@
         <v>235</v>
       </c>
       <c r="L50" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M50" s="38"/>
       <c r="N50" s="38"/>
@@ -6594,7 +6594,7 @@
         <v>235</v>
       </c>
       <c r="L51" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M51" s="38"/>
       <c r="N51" s="38"/>
@@ -6637,7 +6637,7 @@
         <v>235</v>
       </c>
       <c r="L52" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M52" s="38"/>
       <c r="N52" s="38"/>
@@ -7656,7 +7656,7 @@
         <v>235</v>
       </c>
       <c r="L69" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M69" s="38"/>
       <c r="N69" s="38"/>
@@ -7699,7 +7699,7 @@
         <v>235</v>
       </c>
       <c r="L70" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M70" s="38"/>
       <c r="N70" s="38"/>
@@ -7742,7 +7742,7 @@
         <v>235</v>
       </c>
       <c r="L71" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M71" s="38"/>
       <c r="N71" s="38"/>
@@ -7785,7 +7785,7 @@
         <v>235</v>
       </c>
       <c r="L72" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M72" s="38"/>
       <c r="N72" s="38"/>
@@ -7828,7 +7828,7 @@
         <v>235</v>
       </c>
       <c r="L73" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M73" s="38"/>
       <c r="N73" s="38"/>
@@ -7871,7 +7871,7 @@
         <v>235</v>
       </c>
       <c r="L74" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M74" s="38"/>
       <c r="N74" s="38"/>
@@ -7914,7 +7914,7 @@
         <v>235</v>
       </c>
       <c r="L75" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M75" s="38"/>
       <c r="N75" s="38"/>
@@ -7957,7 +7957,7 @@
         <v>235</v>
       </c>
       <c r="L76" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M76" s="38"/>
       <c r="N76" s="38"/>
@@ -8000,7 +8000,7 @@
         <v>235</v>
       </c>
       <c r="L77" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M77" s="38"/>
       <c r="N77" s="38"/>
@@ -8043,7 +8043,7 @@
         <v>235</v>
       </c>
       <c r="L78" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M78" s="38"/>
       <c r="N78" s="38"/>
@@ -8086,7 +8086,7 @@
         <v>235</v>
       </c>
       <c r="L79" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M79" s="38"/>
       <c r="N79" s="38"/>
@@ -8129,7 +8129,7 @@
         <v>235</v>
       </c>
       <c r="L80" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M80" s="38"/>
       <c r="N80" s="38"/>
@@ -8172,7 +8172,7 @@
         <v>235</v>
       </c>
       <c r="L81" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M81" s="38"/>
       <c r="N81" s="38"/>
@@ -8215,7 +8215,7 @@
         <v>235</v>
       </c>
       <c r="L82" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M82" s="38"/>
       <c r="N82" s="38"/>
@@ -8258,7 +8258,7 @@
         <v>235</v>
       </c>
       <c r="L83" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M83" s="38"/>
       <c r="N83" s="38"/>
@@ -8301,7 +8301,7 @@
         <v>235</v>
       </c>
       <c r="L84" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M84" s="38"/>
       <c r="N84" s="38"/>
@@ -8344,7 +8344,7 @@
         <v>235</v>
       </c>
       <c r="L85" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M85" s="38"/>
       <c r="N85" s="38"/>
@@ -8387,7 +8387,7 @@
         <v>235</v>
       </c>
       <c r="L86" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M86" s="38"/>
       <c r="N86" s="38"/>
@@ -8430,7 +8430,7 @@
         <v>235</v>
       </c>
       <c r="L87" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M87" s="38"/>
       <c r="N87" s="38"/>
@@ -8473,7 +8473,7 @@
         <v>235</v>
       </c>
       <c r="L88" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M88" s="38"/>
       <c r="N88" s="38"/>
@@ -8516,7 +8516,7 @@
         <v>235</v>
       </c>
       <c r="L89" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M89" s="38"/>
       <c r="N89" s="38"/>
@@ -8559,7 +8559,7 @@
         <v>235</v>
       </c>
       <c r="L90" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M90" s="38"/>
       <c r="N90" s="38"/>
@@ -8602,7 +8602,7 @@
         <v>235</v>
       </c>
       <c r="L91" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M91" s="38"/>
       <c r="N91" s="38"/>
@@ -8645,7 +8645,7 @@
         <v>235</v>
       </c>
       <c r="L92" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M92" s="38"/>
       <c r="N92" s="38"/>
@@ -8688,7 +8688,7 @@
         <v>235</v>
       </c>
       <c r="L93" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M93" s="38"/>
       <c r="N93" s="38"/>
@@ -8731,7 +8731,7 @@
         <v>235</v>
       </c>
       <c r="L94" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M94" s="38"/>
       <c r="N94" s="38"/>
@@ -8774,7 +8774,7 @@
         <v>235</v>
       </c>
       <c r="L95" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M95" s="38"/>
       <c r="N95" s="38"/>
@@ -8817,7 +8817,7 @@
         <v>235</v>
       </c>
       <c r="L96" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M96" s="38"/>
       <c r="N96" s="38"/>
@@ -8860,7 +8860,7 @@
         <v>235</v>
       </c>
       <c r="L97" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M97" s="38"/>
       <c r="N97" s="38"/>
@@ -8903,7 +8903,7 @@
         <v>235</v>
       </c>
       <c r="L98" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M98" s="38"/>
       <c r="N98" s="38"/>
@@ -8946,7 +8946,7 @@
         <v>235</v>
       </c>
       <c r="L99" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M99" s="38"/>
       <c r="N99" s="38"/>
@@ -8989,7 +8989,7 @@
         <v>235</v>
       </c>
       <c r="L100" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M100" s="38"/>
       <c r="N100" s="38"/>
@@ -9032,7 +9032,7 @@
         <v>235</v>
       </c>
       <c r="L101" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M101" s="38"/>
       <c r="N101" s="38"/>
@@ -9075,7 +9075,7 @@
         <v>235</v>
       </c>
       <c r="L102" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M102" s="38"/>
       <c r="N102" s="38"/>
@@ -9118,7 +9118,7 @@
         <v>235</v>
       </c>
       <c r="L103" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M103" s="38"/>
       <c r="N103" s="38"/>
@@ -9161,7 +9161,7 @@
         <v>235</v>
       </c>
       <c r="L104" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M104" s="38"/>
       <c r="N104" s="38"/>
@@ -9204,7 +9204,7 @@
         <v>235</v>
       </c>
       <c r="L105" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M105" s="38"/>
       <c r="N105" s="38"/>
@@ -9247,7 +9247,7 @@
         <v>235</v>
       </c>
       <c r="L106" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M106" s="38"/>
       <c r="N106" s="38"/>
@@ -9290,7 +9290,7 @@
         <v>235</v>
       </c>
       <c r="L107" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M107" s="38"/>
       <c r="N107" s="38"/>
@@ -9333,7 +9333,7 @@
         <v>235</v>
       </c>
       <c r="L108" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M108" s="38"/>
       <c r="N108" s="38"/>
@@ -9376,7 +9376,7 @@
         <v>235</v>
       </c>
       <c r="L109" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M109" s="38"/>
       <c r="N109" s="38"/>
@@ -9419,7 +9419,7 @@
         <v>235</v>
       </c>
       <c r="L110" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M110" s="38"/>
       <c r="N110" s="38"/>
@@ -9462,7 +9462,7 @@
         <v>235</v>
       </c>
       <c r="L111" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M111" s="38"/>
       <c r="N111" s="38"/>
@@ -9505,7 +9505,7 @@
         <v>235</v>
       </c>
       <c r="L112" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M112" s="38"/>
       <c r="N112" s="38"/>
@@ -9548,7 +9548,7 @@
         <v>235</v>
       </c>
       <c r="L113" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M113" s="38"/>
       <c r="N113" s="38"/>
@@ -9591,7 +9591,7 @@
         <v>235</v>
       </c>
       <c r="L114" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M114" s="38"/>
       <c r="N114" s="38"/>
@@ -9634,7 +9634,7 @@
         <v>235</v>
       </c>
       <c r="L115" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M115" s="38"/>
       <c r="N115" s="38"/>
@@ -9670,13 +9670,13 @@
         <v>45997</v>
       </c>
       <c r="G116" s="37" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="H116" s="37" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="I116" s="42" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="J116" s="38" t="s">
         <v>64</v>
@@ -9702,7 +9702,7 @@
         <v>64</v>
       </c>
       <c r="S116" s="38" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="T116" s="38"/>
       <c r="U116" s="39"/>
@@ -9731,13 +9731,13 @@
         <v>45997</v>
       </c>
       <c r="G117" s="37" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="H117" s="37" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="I117" s="42" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="J117" s="38" t="s">
         <v>64</v>
@@ -9763,7 +9763,7 @@
         <v>64</v>
       </c>
       <c r="S117" s="38" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="T117" s="38"/>
       <c r="U117" s="39"/>
@@ -9792,13 +9792,13 @@
         <v>45997</v>
       </c>
       <c r="G118" s="37" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="H118" s="37" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="I118" s="42" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="J118" s="38" t="s">
         <v>64</v>
@@ -9812,7 +9812,7 @@
         <v>64</v>
       </c>
       <c r="O118" s="38" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="P118" s="38" t="s">
         <v>64</v>
@@ -9824,7 +9824,7 @@
         <v>64</v>
       </c>
       <c r="S118" s="38" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="T118" s="38"/>
       <c r="U118" s="39"/>
@@ -9853,13 +9853,13 @@
         <v>45997</v>
       </c>
       <c r="G119" s="37" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="H119" s="37" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="I119" s="42" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="J119" s="38" t="s">
         <v>64</v>
@@ -9885,7 +9885,7 @@
         <v>64</v>
       </c>
       <c r="S119" s="38" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="T119" s="38"/>
       <c r="U119" s="39"/>
@@ -9914,13 +9914,13 @@
         <v>45997</v>
       </c>
       <c r="G120" s="37" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="H120" s="37" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="I120" s="42" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="J120" s="38" t="s">
         <v>64</v>
@@ -9934,7 +9934,7 @@
         <v>64</v>
       </c>
       <c r="O120" s="38" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="P120" s="38" t="s">
         <v>64</v>
@@ -9946,7 +9946,7 @@
         <v>64</v>
       </c>
       <c r="S120" s="38" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="T120" s="38"/>
       <c r="U120" s="39"/>
@@ -9975,13 +9975,13 @@
         <v>45997</v>
       </c>
       <c r="G121" s="37" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="H121" s="37" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="I121" s="42" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="J121" s="38" t="s">
         <v>64</v>
@@ -10007,7 +10007,7 @@
         <v>64</v>
       </c>
       <c r="S121" s="38" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="T121" s="38"/>
       <c r="U121" s="39"/>
@@ -10036,13 +10036,13 @@
         <v>45997</v>
       </c>
       <c r="G122" s="37" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="H122" s="37" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="I122" s="42" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="J122" s="38" t="s">
         <v>64</v>
@@ -10056,7 +10056,7 @@
         <v>64</v>
       </c>
       <c r="O122" s="38" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="P122" s="38" t="s">
         <v>64</v>
@@ -10068,7 +10068,7 @@
         <v>64</v>
       </c>
       <c r="S122" s="38" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="T122" s="38"/>
       <c r="U122" s="39"/>
@@ -10097,13 +10097,13 @@
         <v>45997</v>
       </c>
       <c r="G123" s="37" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="H123" s="37" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="I123" s="42" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="J123" s="38" t="s">
         <v>64</v>
@@ -10117,7 +10117,7 @@
         <v>64</v>
       </c>
       <c r="O123" s="38" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="P123" s="38" t="s">
         <v>64</v>
@@ -10129,7 +10129,7 @@
         <v>64</v>
       </c>
       <c r="S123" s="38" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="T123" s="38"/>
       <c r="U123" s="39"/>
@@ -10158,13 +10158,13 @@
         <v>45997</v>
       </c>
       <c r="G124" s="37" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="H124" s="37" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="I124" s="42" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="J124" s="38" t="s">
         <v>64</v>
@@ -10178,7 +10178,7 @@
         <v>64</v>
       </c>
       <c r="O124" s="38" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="P124" s="38" t="s">
         <v>64</v>
@@ -10190,7 +10190,7 @@
         <v>64</v>
       </c>
       <c r="S124" s="38" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="T124" s="38"/>
       <c r="U124" s="39"/>
@@ -10219,13 +10219,13 @@
         <v>45997</v>
       </c>
       <c r="G125" s="37" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="H125" s="37" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="I125" s="42" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="J125" s="38" t="s">
         <v>64</v>
@@ -10239,7 +10239,7 @@
         <v>64</v>
       </c>
       <c r="O125" s="38" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="P125" s="38" t="s">
         <v>64</v>
@@ -10251,7 +10251,7 @@
         <v>64</v>
       </c>
       <c r="S125" s="38" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="T125" s="38"/>
       <c r="U125" s="39"/>
@@ -10280,13 +10280,13 @@
         <v>45997</v>
       </c>
       <c r="G126" s="37" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="H126" s="37" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="I126" s="42" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="J126" s="38" t="s">
         <v>64</v>
@@ -10300,7 +10300,7 @@
         <v>64</v>
       </c>
       <c r="O126" s="38" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="P126" s="38" t="s">
         <v>64</v>
@@ -10312,7 +10312,7 @@
         <v>226</v>
       </c>
       <c r="S126" s="38" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="T126" s="38"/>
       <c r="U126" s="39"/>
@@ -10341,13 +10341,13 @@
         <v>45997</v>
       </c>
       <c r="G127" s="37" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="H127" s="37" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="I127" s="42" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="J127" s="38" t="s">
         <v>64</v>
@@ -10361,7 +10361,7 @@
         <v>64</v>
       </c>
       <c r="O127" s="38" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="P127" s="38" t="s">
         <v>64</v>
@@ -10373,7 +10373,7 @@
         <v>64</v>
       </c>
       <c r="S127" s="38" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="T127" s="38"/>
       <c r="U127" s="39"/>
@@ -10402,13 +10402,13 @@
         <v>45997</v>
       </c>
       <c r="G128" s="37" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="H128" s="37" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="I128" s="42" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="J128" s="38" t="s">
         <v>64</v>
@@ -10422,7 +10422,7 @@
         <v>64</v>
       </c>
       <c r="O128" s="38" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="P128" s="38" t="s">
         <v>64</v>
@@ -10434,7 +10434,7 @@
         <v>64</v>
       </c>
       <c r="S128" s="38" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="T128" s="38"/>
       <c r="U128" s="39"/>
@@ -10463,13 +10463,13 @@
         <v>45997</v>
       </c>
       <c r="G129" s="37" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="H129" s="37" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="I129" s="42" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="J129" s="38" t="s">
         <v>64</v>
@@ -10483,7 +10483,7 @@
         <v>64</v>
       </c>
       <c r="O129" s="38" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="P129" s="38" t="s">
         <v>64</v>
@@ -10495,7 +10495,7 @@
         <v>64</v>
       </c>
       <c r="S129" s="38" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="T129" s="38"/>
       <c r="U129" s="39"/>
@@ -10524,13 +10524,13 @@
         <v>45997</v>
       </c>
       <c r="G130" s="37" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="H130" s="37" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="I130" s="42" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="J130" s="38" t="s">
         <v>64</v>
@@ -10544,7 +10544,7 @@
         <v>64</v>
       </c>
       <c r="O130" s="38" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="P130" s="38" t="s">
         <v>64</v>
@@ -10556,7 +10556,7 @@
         <v>64</v>
       </c>
       <c r="S130" s="38" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="T130" s="38"/>
       <c r="U130" s="39"/>
@@ -10592,7 +10592,7 @@
         <v>235</v>
       </c>
       <c r="L131" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M131" s="38"/>
       <c r="N131" s="38"/>
@@ -10635,7 +10635,7 @@
         <v>235</v>
       </c>
       <c r="L132" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M132" s="38"/>
       <c r="N132" s="38"/>
@@ -10678,7 +10678,7 @@
         <v>235</v>
       </c>
       <c r="L133" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M133" s="38"/>
       <c r="N133" s="38"/>
@@ -10721,7 +10721,7 @@
         <v>235</v>
       </c>
       <c r="L134" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M134" s="38"/>
       <c r="N134" s="38"/>
@@ -10764,7 +10764,7 @@
         <v>235</v>
       </c>
       <c r="L135" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M135" s="38"/>
       <c r="N135" s="38"/>
@@ -10807,7 +10807,7 @@
         <v>235</v>
       </c>
       <c r="L136" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M136" s="38"/>
       <c r="N136" s="38"/>
@@ -10850,7 +10850,7 @@
         <v>235</v>
       </c>
       <c r="L137" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M137" s="38"/>
       <c r="N137" s="38"/>
@@ -10893,7 +10893,7 @@
         <v>235</v>
       </c>
       <c r="L138" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M138" s="38"/>
       <c r="N138" s="38"/>
@@ -10936,7 +10936,7 @@
         <v>235</v>
       </c>
       <c r="L139" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M139" s="38"/>
       <c r="N139" s="38"/>
@@ -10979,7 +10979,7 @@
         <v>235</v>
       </c>
       <c r="L140" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M140" s="38"/>
       <c r="N140" s="38"/>
@@ -11022,7 +11022,7 @@
         <v>235</v>
       </c>
       <c r="L141" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M141" s="38"/>
       <c r="N141" s="38"/>
@@ -11065,7 +11065,7 @@
         <v>235</v>
       </c>
       <c r="L142" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M142" s="38"/>
       <c r="N142" s="38"/>
@@ -11108,7 +11108,7 @@
         <v>235</v>
       </c>
       <c r="L143" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M143" s="38"/>
       <c r="N143" s="38"/>
@@ -11151,7 +11151,7 @@
         <v>235</v>
       </c>
       <c r="L144" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M144" s="38"/>
       <c r="N144" s="38"/>
@@ -11194,7 +11194,7 @@
         <v>235</v>
       </c>
       <c r="L145" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M145" s="38"/>
       <c r="N145" s="38"/>
@@ -11237,7 +11237,7 @@
         <v>235</v>
       </c>
       <c r="L146" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M146" s="38"/>
       <c r="N146" s="38"/>
@@ -11280,7 +11280,7 @@
         <v>235</v>
       </c>
       <c r="L147" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M147" s="38"/>
       <c r="N147" s="38"/>
@@ -11323,7 +11323,7 @@
         <v>235</v>
       </c>
       <c r="L148" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M148" s="38"/>
       <c r="N148" s="38"/>
@@ -11366,7 +11366,7 @@
         <v>235</v>
       </c>
       <c r="L149" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M149" s="38"/>
       <c r="N149" s="38"/>
@@ -11409,7 +11409,7 @@
         <v>235</v>
       </c>
       <c r="L150" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M150" s="38"/>
       <c r="N150" s="38"/>
@@ -11452,7 +11452,7 @@
         <v>235</v>
       </c>
       <c r="L151" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M151" s="38"/>
       <c r="N151" s="38"/>
@@ -11495,7 +11495,7 @@
         <v>235</v>
       </c>
       <c r="L152" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M152" s="38"/>
       <c r="N152" s="38"/>
@@ -11538,7 +11538,7 @@
         <v>235</v>
       </c>
       <c r="L153" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M153" s="38" t="s">
         <v>64</v>
@@ -11593,7 +11593,7 @@
         <v>235</v>
       </c>
       <c r="L154" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M154" s="38"/>
       <c r="N154" s="38"/>
@@ -11636,7 +11636,7 @@
         <v>235</v>
       </c>
       <c r="L155" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M155" s="38"/>
       <c r="N155" s="38"/>
@@ -11679,7 +11679,7 @@
         <v>235</v>
       </c>
       <c r="L156" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M156" s="38"/>
       <c r="N156" s="38"/>
@@ -11722,7 +11722,7 @@
         <v>235</v>
       </c>
       <c r="L157" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M157" s="38"/>
       <c r="N157" s="38"/>
@@ -11765,7 +11765,7 @@
         <v>235</v>
       </c>
       <c r="L158" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M158" s="38"/>
       <c r="N158" s="38"/>
@@ -11808,7 +11808,7 @@
         <v>235</v>
       </c>
       <c r="L159" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M159" s="38"/>
       <c r="N159" s="38"/>
@@ -11851,7 +11851,7 @@
         <v>235</v>
       </c>
       <c r="L160" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M160" s="38"/>
       <c r="N160" s="38"/>
@@ -11894,7 +11894,7 @@
         <v>235</v>
       </c>
       <c r="L161" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M161" s="38"/>
       <c r="N161" s="38"/>
@@ -11937,7 +11937,7 @@
         <v>235</v>
       </c>
       <c r="L162" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M162" s="38"/>
       <c r="N162" s="38"/>
@@ -11980,7 +11980,7 @@
         <v>235</v>
       </c>
       <c r="L163" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M163" s="38"/>
       <c r="N163" s="38"/>
@@ -12013,16 +12013,16 @@
         <v>379</v>
       </c>
       <c r="F164" s="47">
-        <v>45997</v>
+        <v>46087</v>
       </c>
       <c r="G164" s="37" t="s">
-        <v>582</v>
+        <v>600</v>
       </c>
       <c r="H164" s="37" t="s">
-        <v>583</v>
+        <v>601</v>
       </c>
       <c r="I164" s="42" t="s">
-        <v>584</v>
+        <v>602</v>
       </c>
       <c r="J164" s="38" t="s">
         <v>64</v>
@@ -12060,16 +12060,16 @@
         <v>380</v>
       </c>
       <c r="F165" s="47">
-        <v>45997</v>
+        <v>46087</v>
       </c>
       <c r="G165" s="37" t="s">
-        <v>585</v>
+        <v>603</v>
       </c>
       <c r="H165" s="37" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="I165" s="42" t="s">
-        <v>587</v>
+        <v>605</v>
       </c>
       <c r="J165" s="38" t="s">
         <v>64</v>
@@ -12117,7 +12117,7 @@
         <v>235</v>
       </c>
       <c r="L166" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M166" s="38"/>
       <c r="N166" s="38"/>
@@ -12160,7 +12160,7 @@
         <v>235</v>
       </c>
       <c r="L167" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M167" s="38"/>
       <c r="N167" s="38"/>
@@ -12203,7 +12203,7 @@
         <v>235</v>
       </c>
       <c r="L168" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M168" s="38"/>
       <c r="N168" s="38"/>
@@ -12246,7 +12246,7 @@
         <v>235</v>
       </c>
       <c r="L169" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M169" s="38"/>
       <c r="N169" s="38"/>
@@ -12289,7 +12289,7 @@
         <v>235</v>
       </c>
       <c r="L170" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M170" s="38"/>
       <c r="N170" s="38"/>
@@ -12332,7 +12332,7 @@
         <v>235</v>
       </c>
       <c r="L171" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M171" s="38"/>
       <c r="N171" s="38"/>
@@ -12375,7 +12375,7 @@
         <v>235</v>
       </c>
       <c r="L172" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M172" s="38"/>
       <c r="N172" s="38"/>
@@ -12418,7 +12418,7 @@
         <v>235</v>
       </c>
       <c r="L173" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M173" s="38"/>
       <c r="N173" s="38"/>
@@ -12461,7 +12461,7 @@
         <v>235</v>
       </c>
       <c r="L174" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M174" s="38"/>
       <c r="N174" s="38"/>
@@ -12504,7 +12504,7 @@
         <v>235</v>
       </c>
       <c r="L175" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M175" s="38"/>
       <c r="N175" s="38"/>
@@ -12540,13 +12540,13 @@
         <v>45997</v>
       </c>
       <c r="G176" s="35" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="H176" s="35" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="I176" s="35" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="J176" s="38" t="s">
         <v>64</v>
@@ -12560,7 +12560,7 @@
         <v>64</v>
       </c>
       <c r="O176" s="35" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="P176" s="38" t="s">
         <v>64</v>
@@ -12669,7 +12669,7 @@
         <v>235</v>
       </c>
       <c r="L178" s="35" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M178" s="38"/>
       <c r="N178" s="38"/>
@@ -12712,7 +12712,7 @@
         <v>235</v>
       </c>
       <c r="L179" s="35" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M179" s="38"/>
       <c r="N179" s="38"/>
@@ -12755,7 +12755,7 @@
         <v>235</v>
       </c>
       <c r="L180" s="35" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M180" s="38"/>
       <c r="N180" s="38"/>
@@ -12798,7 +12798,7 @@
         <v>235</v>
       </c>
       <c r="L181" s="35" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M181" s="38"/>
       <c r="N181" s="38"/>
@@ -12841,7 +12841,7 @@
         <v>235</v>
       </c>
       <c r="L182" s="35" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M182" s="38"/>
       <c r="N182" s="38"/>
@@ -12877,13 +12877,13 @@
         <v>45997</v>
       </c>
       <c r="G183" s="35" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="H183" s="35" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="I183" s="35" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="J183" s="38" t="s">
         <v>64</v>
@@ -12897,7 +12897,7 @@
         <v>64</v>
       </c>
       <c r="O183" s="35" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="P183" s="38" t="s">
         <v>64</v>
@@ -12909,7 +12909,7 @@
         <v>64</v>
       </c>
       <c r="S183" s="35" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="T183" s="38"/>
       <c r="U183" s="35"/>
@@ -12945,7 +12945,7 @@
         <v>235</v>
       </c>
       <c r="L184" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M184" s="38"/>
       <c r="N184" s="38"/>
@@ -12988,7 +12988,7 @@
         <v>235</v>
       </c>
       <c r="L185" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M185" s="38"/>
       <c r="N185" s="38"/>
@@ -13021,16 +13021,16 @@
         <v>410</v>
       </c>
       <c r="F186" s="47">
-        <v>45997</v>
+        <v>46087</v>
       </c>
       <c r="G186" s="37" t="s">
-        <v>513</v>
+        <v>606</v>
       </c>
       <c r="H186" s="37" t="s">
-        <v>514</v>
+        <v>607</v>
       </c>
       <c r="I186" s="42" t="s">
-        <v>515</v>
+        <v>608</v>
       </c>
       <c r="J186" s="38" t="s">
         <v>64</v>
@@ -13051,7 +13051,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="187" spans="1:23" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:23" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="35">
         <v>472</v>
       </c>
@@ -13068,16 +13068,16 @@
         <v>414</v>
       </c>
       <c r="F187" s="47">
-        <v>45997</v>
+        <v>46087</v>
       </c>
       <c r="G187" s="37" t="s">
-        <v>516</v>
+        <v>609</v>
       </c>
       <c r="H187" s="37" t="s">
-        <v>517</v>
+        <v>610</v>
       </c>
       <c r="I187" s="42" t="s">
-        <v>518</v>
+        <v>611</v>
       </c>
       <c r="J187" s="38" t="s">
         <v>64</v>
@@ -13125,7 +13125,7 @@
         <v>235</v>
       </c>
       <c r="L188" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M188" s="38"/>
       <c r="N188" s="38"/>
@@ -13161,13 +13161,13 @@
         <v>45997</v>
       </c>
       <c r="G189" s="37" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="H189" s="37" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="I189" s="42" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="J189" s="38" t="s">
         <v>64</v>
@@ -13181,7 +13181,7 @@
         <v>64</v>
       </c>
       <c r="O189" s="38" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="P189" s="38" t="s">
         <v>64</v>
@@ -13193,7 +13193,7 @@
         <v>64</v>
       </c>
       <c r="S189" s="38" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="T189" s="38"/>
       <c r="U189" s="39"/>
@@ -13222,13 +13222,13 @@
         <v>45997</v>
       </c>
       <c r="G190" s="37" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="H190" s="37" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="I190" s="42" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="J190" s="38" t="s">
         <v>64</v>
@@ -13242,7 +13242,7 @@
         <v>64</v>
       </c>
       <c r="O190" s="38" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="P190" s="38" t="s">
         <v>64</v>
@@ -13254,7 +13254,7 @@
         <v>64</v>
       </c>
       <c r="S190" s="38" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="T190" s="38"/>
       <c r="U190" s="39"/>
@@ -13290,7 +13290,7 @@
         <v>235</v>
       </c>
       <c r="L191" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M191" s="38"/>
       <c r="N191" s="38"/>
@@ -13333,7 +13333,7 @@
         <v>235</v>
       </c>
       <c r="L192" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M192" s="38"/>
       <c r="N192" s="38"/>
@@ -13376,7 +13376,7 @@
         <v>235</v>
       </c>
       <c r="L193" s="38" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="M193" s="38"/>
       <c r="N193" s="38"/>
@@ -17352,8 +17352,7 @@
   <autoFilter ref="A9:W193" xr:uid="{00000000-0001-0000-0200-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="31"/>
-        <filter val="39"/>
+        <filter val="472"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -19626,12 +19625,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19779,15 +19775,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -19811,18 +19819,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GATEWAY/S1#111#JOINSOFTSRLXX/Joinsoft_Srl/Gestione_Stabilimenti_Termali/Ver_6.31/report-checklist.xlsx
+++ b/GATEWAY/S1#111#JOINSOFTSRLXX/Joinsoft_Srl/Gestione_Stabilimenti_Termali/Ver_6.31/report-checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francesco\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE373560-8C7C-4553-BB0A-5A2B3BD6F4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191072ED-FCC0-4F08-A4D2-44197A81C0D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3075" yWindow="-13620" windowWidth="21840" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2185,30 +2185,6 @@
     <t>subject_application_version:Ver_6.31</t>
   </si>
   <si>
-    <t>2026-02-27T16:32:16.677Z</t>
-  </si>
-  <si>
-    <t>838685cc01a13a1efe5a36388670f143</t>
-  </si>
-  <si>
-    <t>2026-02-27T16:32:17.189Z</t>
-  </si>
-  <si>
-    <t>be3344b8fc9c13806e1fb482d6be03b7</t>
-  </si>
-  <si>
-    <t>a98d424da5e5f014ad54cf257883d086</t>
-  </si>
-  <si>
-    <t>2026-02-27T16:35:30.282Z</t>
-  </si>
-  <si>
-    <t>2026-02-27T16:35:30.775Z</t>
-  </si>
-  <si>
-    <t>96ba6135629f789eb2778a43f8b6c7d7</t>
-  </si>
-  <si>
     <t>2026-03-06T15:51:09.943Z</t>
   </si>
   <si>
@@ -2243,6 +2219,30 @@
   </si>
   <si>
     <t>2.16.840.1.113883.2.9.2.120.4.4.4175a3ea5c2a8ebacb9146e63da90f5141633abd7cbb86ef4630d25f17280334.6dc48e4501^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-18T15:05:13.243Z</t>
+  </si>
+  <si>
+    <t>2026-03-18T15:05:13.650Z</t>
+  </si>
+  <si>
+    <t>69abb61e8321e7c0669e758e7017027d</t>
+  </si>
+  <si>
+    <t>2d5208549145c251d8a82813e72a9885</t>
+  </si>
+  <si>
+    <t>2026-03-18T15:03:34.512Z</t>
+  </si>
+  <si>
+    <t>2026-03-18T15:03:34.902Z</t>
+  </si>
+  <si>
+    <t>3dd22bee674c4d596827c21cec1f1d65</t>
+  </si>
+  <si>
+    <t>2191dcd5e052e59d873f96feb5ac1f20</t>
   </si>
 </sst>
 </file>
@@ -4786,7 +4786,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="11.1" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="35">
         <v>31</v>
       </c>
@@ -4803,13 +4803,13 @@
         <v>43</v>
       </c>
       <c r="F14" s="47">
-        <v>45997</v>
+        <v>46099</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="I14" s="42" t="s">
         <v>439</v>
@@ -4864,13 +4864,13 @@
         <v>43</v>
       </c>
       <c r="F15" s="47">
-        <v>45997</v>
+        <v>46099</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>593</v>
+        <v>606</v>
       </c>
       <c r="I15" s="42" t="s">
         <v>439</v>
@@ -5166,7 +5166,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="11.1" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="35">
         <v>39</v>
       </c>
@@ -5183,13 +5183,13 @@
         <v>55</v>
       </c>
       <c r="F22" s="47">
-        <v>45997</v>
+        <v>46099</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>598</v>
+        <v>609</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="I22" s="42" t="s">
         <v>439</v>
@@ -5244,13 +5244,13 @@
         <v>55</v>
       </c>
       <c r="F23" s="47">
-        <v>45997</v>
+        <v>46099</v>
       </c>
       <c r="G23" s="37" t="s">
-        <v>594</v>
+        <v>605</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="I23" s="42" t="s">
         <v>439</v>
@@ -12016,13 +12016,13 @@
         <v>46087</v>
       </c>
       <c r="G164" s="37" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="H164" s="37" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="I164" s="42" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="J164" s="38" t="s">
         <v>64</v>
@@ -12063,13 +12063,13 @@
         <v>46087</v>
       </c>
       <c r="G165" s="37" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="H165" s="37" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="I165" s="42" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="J165" s="38" t="s">
         <v>64</v>
@@ -13024,13 +13024,13 @@
         <v>46087</v>
       </c>
       <c r="G186" s="37" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="H186" s="37" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="I186" s="42" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="J186" s="38" t="s">
         <v>64</v>
@@ -13051,7 +13051,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="187" spans="1:23" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:23" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="35">
         <v>472</v>
       </c>
@@ -13071,13 +13071,13 @@
         <v>46087</v>
       </c>
       <c r="G187" s="37" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="H187" s="37" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I187" s="42" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="J187" s="38" t="s">
         <v>64</v>
@@ -17352,7 +17352,8 @@
   <autoFilter ref="A9:W193" xr:uid="{00000000-0001-0000-0200-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="472"/>
+        <filter val="31"/>
+        <filter val="39"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -19625,9 +19626,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19775,27 +19779,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -19819,9 +19811,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GATEWAY/S1#111#JOINSOFTSRLXX/Joinsoft_Srl/Gestione_Stabilimenti_Termali/Ver_6.31/report-checklist.xlsx
+++ b/GATEWAY/S1#111#JOINSOFTSRLXX/Joinsoft_Srl/Gestione_Stabilimenti_Termali/Ver_6.31/report-checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francesco\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191072ED-FCC0-4F08-A4D2-44197A81C0D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C71ACE-9B70-465E-84F3-E7505B14DD0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="-13620" windowWidth="21840" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -2179,9 +2179,6 @@
     <t>subject_application_id: Gestione_Stabilimenti_Termali</t>
   </si>
   <si>
-    <t>subject_application_vendor:JoinSoft_Srl</t>
-  </si>
-  <si>
     <t>subject_application_version:Ver_6.31</t>
   </si>
   <si>
@@ -2243,6 +2240,9 @@
   </si>
   <si>
     <t>2191dcd5e052e59d873f96feb5ac1f20</t>
+  </si>
+  <si>
+    <t>subject_application_vendor:Joinsoft_Srl</t>
   </si>
 </sst>
 </file>
@@ -4428,7 +4428,7 @@
       <c r="A4" s="57"/>
       <c r="B4" s="58"/>
       <c r="C4" s="61" t="s">
-        <v>590</v>
+        <v>611</v>
       </c>
       <c r="D4" s="53"/>
       <c r="E4" s="4"/>
@@ -4455,7 +4455,7 @@
       <c r="A5" s="59"/>
       <c r="B5" s="60"/>
       <c r="C5" s="61" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D5" s="53"/>
       <c r="F5" s="6"/>
@@ -4806,10 +4806,10 @@
         <v>46099</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="I14" s="42" t="s">
         <v>439</v>
@@ -4867,10 +4867,10 @@
         <v>46099</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I15" s="42" t="s">
         <v>439</v>
@@ -5186,10 +5186,10 @@
         <v>46099</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="I22" s="42" t="s">
         <v>439</v>
@@ -5247,10 +5247,10 @@
         <v>46099</v>
       </c>
       <c r="G23" s="37" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I23" s="42" t="s">
         <v>439</v>
@@ -12016,13 +12016,13 @@
         <v>46087</v>
       </c>
       <c r="G164" s="37" t="s">
+        <v>591</v>
+      </c>
+      <c r="H164" s="37" t="s">
         <v>592</v>
       </c>
-      <c r="H164" s="37" t="s">
+      <c r="I164" s="42" t="s">
         <v>593</v>
-      </c>
-      <c r="I164" s="42" t="s">
-        <v>594</v>
       </c>
       <c r="J164" s="38" t="s">
         <v>64</v>
@@ -12063,13 +12063,13 @@
         <v>46087</v>
       </c>
       <c r="G165" s="37" t="s">
+        <v>594</v>
+      </c>
+      <c r="H165" s="37" t="s">
         <v>595</v>
       </c>
-      <c r="H165" s="37" t="s">
+      <c r="I165" s="42" t="s">
         <v>596</v>
-      </c>
-      <c r="I165" s="42" t="s">
-        <v>597</v>
       </c>
       <c r="J165" s="38" t="s">
         <v>64</v>
@@ -13024,13 +13024,13 @@
         <v>46087</v>
       </c>
       <c r="G186" s="37" t="s">
+        <v>597</v>
+      </c>
+      <c r="H186" s="37" t="s">
         <v>598</v>
       </c>
-      <c r="H186" s="37" t="s">
+      <c r="I186" s="42" t="s">
         <v>599</v>
-      </c>
-      <c r="I186" s="42" t="s">
-        <v>600</v>
       </c>
       <c r="J186" s="38" t="s">
         <v>64</v>
@@ -13071,13 +13071,13 @@
         <v>46087</v>
       </c>
       <c r="G187" s="37" t="s">
+        <v>600</v>
+      </c>
+      <c r="H187" s="37" t="s">
         <v>601</v>
       </c>
-      <c r="H187" s="37" t="s">
+      <c r="I187" s="42" t="s">
         <v>602</v>
-      </c>
-      <c r="I187" s="42" t="s">
-        <v>603</v>
       </c>
       <c r="J187" s="38" t="s">
         <v>64</v>
@@ -19626,12 +19626,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19779,15 +19776,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -19811,18 +19820,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GATEWAY/S1#111#JOINSOFTSRLXX/Joinsoft_Srl/Gestione_Stabilimenti_Termali/Ver_6.31/report-checklist.xlsx
+++ b/GATEWAY/S1#111#JOINSOFTSRLXX/Joinsoft_Srl/Gestione_Stabilimenti_Termali/Ver_6.31/report-checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francesco\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36C71ACE-9B70-465E-84F3-E7505B14DD0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8D5D9A-1C9D-4C7C-86E7-063C459D49A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2182,42 +2182,6 @@
     <t>subject_application_version:Ver_6.31</t>
   </si>
   <si>
-    <t>2026-03-06T15:51:09.943Z</t>
-  </si>
-  <si>
-    <t>aac2e7cb1c7c3220122b8f591a73f015</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.f7b894b3a81cc99665fc11da1b86dda52777a974623d939bd318c0d392bee9da.78152d74d0^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-06T15:51:11.318Z</t>
-  </si>
-  <si>
-    <t>33bc6c11aa1433ec8659f2ee16c2a8f5</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.dfe47c5b669ed6d03ff3e464f0b7a7ddb65109bf84965676e19a287e378c758e.b3c02e9078^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-06T15:51:13.077Z</t>
-  </si>
-  <si>
-    <t>ae502d87b446230ce2bc7347fb7ad747</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.117789eb8e22f6c94d31a40b7b9b3f5c4589c6c9ab03133d13360782f1b8a150.8c45f7d9bc^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-06T15:51:14.652Z</t>
-  </si>
-  <si>
-    <t>af1a8db82c7ecf940c9729bf84976d15</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.4175a3ea5c2a8ebacb9146e63da90f5141633abd7cbb86ef4630d25f17280334.6dc48e4501^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>2026-03-18T15:05:13.243Z</t>
   </si>
   <si>
@@ -2243,6 +2207,42 @@
   </si>
   <si>
     <t>subject_application_vendor:Joinsoft_Srl</t>
+  </si>
+  <si>
+    <t>2026-03-25T08:16:23.614Z</t>
+  </si>
+  <si>
+    <t>08e3c279c37f6ba61f69dd9e2fa2f60e</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.0ab541df2fccb2d9ccd6c5af009ab97c1739337983a95b9f75c864f2b3be6d91.aaf3c21f15^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-25T08:16:24.491Z</t>
+  </si>
+  <si>
+    <t>12ebdfc2aebf6b8a6ebda2d147df9887</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.c14e8b1bfef36f6f2b3d891d73399882c9dc8bdaa9903a9d2190c18ebe8c50e3.853716450e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-25T08:16:25.323Z</t>
+  </si>
+  <si>
+    <t>61ae34489496b89fdd9484fc6413dbd4</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.9f8f38100155863f456fd3d087e733ce5ca0cc2821d2afd2d421e6634748b701.bdfff4f7ab^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-25T08:16:26.114Z</t>
+  </si>
+  <si>
+    <t>b5330938e686802afba7197238e5832f</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.a6b7f56520b0f47b553d484c4e3b9f6b6dde76ca191e6da490ac9cdb89392068.674db9706a^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -4428,7 +4428,7 @@
       <c r="A4" s="57"/>
       <c r="B4" s="58"/>
       <c r="C4" s="61" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="D4" s="53"/>
       <c r="E4" s="4"/>
@@ -4786,7 +4786,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" ht="11.1" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="35">
         <v>31</v>
       </c>
@@ -4806,10 +4806,10 @@
         <v>46099</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="I14" s="42" t="s">
         <v>439</v>
@@ -4867,10 +4867,10 @@
         <v>46099</v>
       </c>
       <c r="G15" s="37" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="I15" s="42" t="s">
         <v>439</v>
@@ -5166,7 +5166,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:23" ht="11.1" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="35">
         <v>39</v>
       </c>
@@ -5186,10 +5186,10 @@
         <v>46099</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="I22" s="42" t="s">
         <v>439</v>
@@ -5247,10 +5247,10 @@
         <v>46099</v>
       </c>
       <c r="G23" s="37" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="I23" s="42" t="s">
         <v>439</v>
@@ -12013,16 +12013,16 @@
         <v>379</v>
       </c>
       <c r="F164" s="47">
-        <v>46087</v>
+        <v>46106</v>
       </c>
       <c r="G164" s="37" t="s">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="H164" s="37" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="I164" s="42" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="J164" s="38" t="s">
         <v>64</v>
@@ -12060,16 +12060,16 @@
         <v>380</v>
       </c>
       <c r="F165" s="47">
-        <v>46087</v>
+        <v>46106</v>
       </c>
       <c r="G165" s="37" t="s">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="H165" s="37" t="s">
-        <v>595</v>
+        <v>604</v>
       </c>
       <c r="I165" s="42" t="s">
-        <v>596</v>
+        <v>605</v>
       </c>
       <c r="J165" s="38" t="s">
         <v>64</v>
@@ -13021,16 +13021,16 @@
         <v>410</v>
       </c>
       <c r="F186" s="47">
-        <v>46087</v>
+        <v>46106</v>
       </c>
       <c r="G186" s="37" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="H186" s="37" t="s">
-        <v>598</v>
+        <v>607</v>
       </c>
       <c r="I186" s="42" t="s">
-        <v>599</v>
+        <v>608</v>
       </c>
       <c r="J186" s="38" t="s">
         <v>64</v>
@@ -13051,7 +13051,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="187" spans="1:23" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:23" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="35">
         <v>472</v>
       </c>
@@ -13068,16 +13068,16 @@
         <v>414</v>
       </c>
       <c r="F187" s="47">
-        <v>46087</v>
+        <v>46106</v>
       </c>
       <c r="G187" s="37" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="H187" s="37" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="I187" s="42" t="s">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="J187" s="38" t="s">
         <v>64</v>
@@ -17352,8 +17352,7 @@
   <autoFilter ref="A9:W193" xr:uid="{00000000-0001-0000-0200-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="31"/>
-        <filter val="39"/>
+        <filter val="472"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -19626,9 +19625,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19776,27 +19778,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -19820,9 +19810,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GATEWAY/S1#111#JOINSOFTSRLXX/Joinsoft_Srl/Gestione_Stabilimenti_Termali/Ver_6.31/report-checklist.xlsx
+++ b/GATEWAY/S1#111#JOINSOFTSRLXX/Joinsoft_Srl/Gestione_Stabilimenti_Termali/Ver_6.31/report-checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francesco\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8D5D9A-1C9D-4C7C-86E7-063C459D49A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3BDD04-DC85-4022-BDF1-622FEB946ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3075" yWindow="-13620" windowWidth="21840" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -2218,15 +2218,6 @@
     <t>2.16.840.1.113883.2.9.2.120.4.4.0ab541df2fccb2d9ccd6c5af009ab97c1739337983a95b9f75c864f2b3be6d91.aaf3c21f15^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
-    <t>2026-03-25T08:16:24.491Z</t>
-  </si>
-  <si>
-    <t>12ebdfc2aebf6b8a6ebda2d147df9887</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.c14e8b1bfef36f6f2b3d891d73399882c9dc8bdaa9903a9d2190c18ebe8c50e3.853716450e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>2026-03-25T08:16:25.323Z</t>
   </si>
   <si>
@@ -2236,13 +2227,22 @@
     <t>2.16.840.1.113883.2.9.2.120.4.4.9f8f38100155863f456fd3d087e733ce5ca0cc2821d2afd2d421e6634748b701.bdfff4f7ab^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
-    <t>2026-03-25T08:16:26.114Z</t>
-  </si>
-  <si>
-    <t>b5330938e686802afba7197238e5832f</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.a6b7f56520b0f47b553d484c4e3b9f6b6dde76ca191e6da490ac9cdb89392068.674db9706a^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-03-26T10:48:38.618Z</t>
+  </si>
+  <si>
+    <t>05bc761170cd807475bccbfad15d2f9b</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.7cba0fe9ddcb13ec116289dec5aee787f34669b61f5c77579b24c014b72c3671.d249bf7896^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-26T10:48:37.517Z</t>
+  </si>
+  <si>
+    <t>95f5b589ea7dd17ed618b51746249d25</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.1564e1cd5a436803ffc2630cb90cde970aa196856e93241d1ab81e12533fbfba.524235aac1^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -12043,7 +12043,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="165" spans="1:23" ht="11.1" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="35">
         <v>449</v>
       </c>
@@ -12060,16 +12060,16 @@
         <v>380</v>
       </c>
       <c r="F165" s="47">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="G165" s="37" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="H165" s="37" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="I165" s="42" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="J165" s="38" t="s">
         <v>64</v>
@@ -13024,13 +13024,13 @@
         <v>46106</v>
       </c>
       <c r="G186" s="37" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="H186" s="37" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="I186" s="42" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="J186" s="38" t="s">
         <v>64</v>
@@ -13051,7 +13051,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="187" spans="1:23" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:23" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="35">
         <v>472</v>
       </c>
@@ -13068,16 +13068,16 @@
         <v>414</v>
       </c>
       <c r="F187" s="47">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="G187" s="37" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="H187" s="37" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="I187" s="42" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="J187" s="38" t="s">
         <v>64</v>
@@ -17352,7 +17352,7 @@
   <autoFilter ref="A9:W193" xr:uid="{00000000-0001-0000-0200-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="472"/>
+        <filter val="449"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -17371,7 +17371,7 @@
   <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{F5F4AC7B-142E-4F14-AD0B-95E75DB6B433}">
           <x14:formula1>
             <xm:f>Sheet1!$B$2:$B$3</xm:f>
@@ -19625,12 +19625,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19778,15 +19775,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -19810,18 +19819,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GATEWAY/S1#111#JOINSOFTSRLXX/Joinsoft_Srl/Gestione_Stabilimenti_Termali/Ver_6.31/report-checklist.xlsx
+++ b/GATEWAY/S1#111#JOINSOFTSRLXX/Joinsoft_Srl/Gestione_Stabilimenti_Termali/Ver_6.31/report-checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francesco\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3BDD04-DC85-4022-BDF1-622FEB946ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C99A7E-8ED8-40DA-B8E2-F1C1CFDA2BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3075" yWindow="-13620" windowWidth="21840" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1966" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1967" uniqueCount="613">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -2227,22 +2227,25 @@
     <t>2.16.840.1.113883.2.9.2.120.4.4.9f8f38100155863f456fd3d087e733ce5ca0cc2821d2afd2d421e6634748b701.bdfff4f7ab^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
-    <t>2026-03-26T10:48:38.618Z</t>
-  </si>
-  <si>
-    <t>05bc761170cd807475bccbfad15d2f9b</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.7cba0fe9ddcb13ec116289dec5aee787f34669b61f5c77579b24c014b72c3671.d249bf7896^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>2026-03-26T10:48:37.517Z</t>
   </si>
   <si>
-    <t>95f5b589ea7dd17ed618b51746249d25</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.1564e1cd5a436803ffc2630cb90cde970aa196856e93241d1ab81e12533fbfba.524235aac1^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-03-27T14:19:37.158Z</t>
+  </si>
+  <si>
+    <t>f0beb8544ce3d6f25a8486e30bfd80e0</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.7010d1ae0fc4062acd6f9bb843777bca295f2a29ef8505d3f06c97776d7d061c.d9503ae63c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-27T14:19:38.117Z</t>
+  </si>
+  <si>
+    <t>ace0fcadb12b69eff8ba8dc934560a64</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.986bbccfc3795bffb220c7521c24e9a09383d8ca864ea8c4be9857baeefb69ba.199d7c5840^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -12043,7 +12046,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="165" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:23" ht="11.1" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="35">
         <v>449</v>
       </c>
@@ -12059,17 +12062,17 @@
       <c r="E165" s="43" t="s">
         <v>380</v>
       </c>
-      <c r="F165" s="47">
-        <v>46107</v>
+      <c r="F165" s="47" t="s">
+        <v>607</v>
       </c>
       <c r="G165" s="37" t="s">
+        <v>606</v>
+      </c>
+      <c r="H165" s="37" t="s">
+        <v>608</v>
+      </c>
+      <c r="I165" s="42" t="s">
         <v>609</v>
-      </c>
-      <c r="H165" s="37" t="s">
-        <v>610</v>
-      </c>
-      <c r="I165" s="42" t="s">
-        <v>611</v>
       </c>
       <c r="J165" s="38" t="s">
         <v>64</v>
@@ -13051,7 +13054,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="187" spans="1:23" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:23" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="35">
         <v>472</v>
       </c>
@@ -13068,16 +13071,16 @@
         <v>414</v>
       </c>
       <c r="F187" s="47">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="G187" s="37" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="H187" s="37" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="I187" s="42" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="J187" s="38" t="s">
         <v>64</v>
@@ -17352,7 +17355,7 @@
   <autoFilter ref="A9:W193" xr:uid="{00000000-0001-0000-0200-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="449"/>
+        <filter val="472"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -19625,9 +19628,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19775,27 +19781,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -19819,9 +19813,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
